--- a/artfynd/A 30558-2025 artfynd.xlsx
+++ b/artfynd/A 30558-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103013093</v>
+        <v>135217161</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
+        <v>92220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Giertsåive, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600843</v>
+        <v>600827</v>
       </c>
       <c r="R2" t="n">
-        <v>7287391</v>
+        <v>7287406</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,15 +770,702 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135217162</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>600827</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7287406</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135217160</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>600836</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7287397</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135217154</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600775</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7287249</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135217157</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600772</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7287363</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135217153</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57925</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>600918</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7287229</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103013093</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>600843</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7287391</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Benita Martinsdotter</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Benita Martinsdotter</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30558-2025 artfynd.xlsx
+++ b/artfynd/A 30558-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217161</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217162</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217160</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1121,6 +1141,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217154</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217157</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217153</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1466,8 +1501,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103013093</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30558-2025 artfynd.xlsx
+++ b/artfynd/A 30558-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135217161</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135217162</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135217160</v>
       </c>
       <c r="B4" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135217154</v>
       </c>
       <c r="B5" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135217157</v>
       </c>
       <c r="B6" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135217153</v>
       </c>
       <c r="B7" t="n">
-        <v>57925</v>
+        <v>57930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 30558-2025 artfynd.xlsx
+++ b/artfynd/A 30558-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135217161</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135217162</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135217160</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135217154</v>
       </c>
       <c r="B5" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135217157</v>
       </c>
       <c r="B6" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 30558-2025 artfynd.xlsx
+++ b/artfynd/A 30558-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,59 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103013093</v>
+        <v>135217161</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Giertsåive, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600843</v>
+        <v>600827</v>
       </c>
       <c r="R2" t="n">
-        <v>7287391</v>
+        <v>7287406</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,16 +775,733 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217161</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135217162</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>353</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>600827</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7287406</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217162</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135217160</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92101</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>600836</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7287397</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217160</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135217154</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>600775</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7287249</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217154</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135217157</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>600772</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7287363</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217157</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135217153</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57930</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Giertsåive, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>600918</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7287229</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135217153</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103013093</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>600843</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7287391</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Benita Martinsdotter</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Benita Martinsdotter</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/103013093</t>
         </is>
@@ -804,6 +1510,12 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30558-2025 artfynd.xlsx
+++ b/artfynd/A 30558-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135217161</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>135217160</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
